--- a/cake-warehouse/karta-sklada.xlsx
+++ b/cake-warehouse/karta-sklada.xlsx
@@ -494,7 +494,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Встаньте у двери и идите против часовой стрелки. Первое место — 1, следующее — 2 и так далее. Впишите номер места в жёлтую колонку для каждого товара. Несколько товаров на одном месте — один номер. Товар не стоит на складе — оставьте пусто.</t>
+          <t>Встаньте у двери и идите по часовой стрелке. Первое место — 1, следующее — 2 и так далее. Впишите номер места в жёлтую колонку для каждого товара. Несколько товаров на одном месте — один номер. Товар не стоит на складе — оставьте пусто.</t>
         </is>
       </c>
     </row>
